--- a/docs/wiring/signals_split_v8.xlsx
+++ b/docs/wiring/signals_split_v8.xlsx
@@ -496,14 +496,14 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>S4-* = CP4, S5-* = CP5, S6-* = CP6. Mast is filled only when v8 routes</t>
+          <t>Upper-deck plants are Switch 61, 63, 65…; heads are 62L, 64R, 66RA….</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>make a 2-head grouping obvious; otherwise the row is a defined head.</t>
+          <t>S4-* = CP4, S5-* = CP5, S6-* = CP6 (historical IDs kept in Notes as was S4-1).</t>
         </is>
       </c>
     </row>
@@ -9716,22 +9716,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SW129</t>
+          <t>Switch 67</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9788,12 +9788,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10628,12 +10628,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>64R</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10828,12 +10828,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -10873,7 +10873,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11093,12 +11093,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11163,12 +11163,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11353,12 +11353,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S4-2</t>
+          <t>68L</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11678,12 +11678,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -11748,12 +11748,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -11788,12 +11788,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -11873,12 +11873,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -11918,12 +11918,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -11978,12 +11978,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -12173,12 +12173,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -12243,12 +12243,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -12313,12 +12313,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12333,12 +12333,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -12378,12 +12378,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -12398,12 +12398,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -12448,12 +12448,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12468,12 +12468,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -12518,12 +12518,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12538,12 +12538,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -12653,12 +12653,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -12723,12 +12723,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>64L</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -12928,17 +12928,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -12953,12 +12953,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -12993,17 +12993,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -13063,17 +13063,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -13133,17 +13133,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -13158,12 +13158,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -13198,17 +13198,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -13268,17 +13268,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -13293,12 +13293,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -13338,17 +13338,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -13363,12 +13363,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -13403,17 +13403,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -13428,12 +13428,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -13473,17 +13473,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -13543,17 +13543,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -13608,17 +13608,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -13633,12 +13633,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -13678,17 +13678,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S4-4</t>
+          <t>66RA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SW138 (with S4-5)</t>
+          <t>Switch 65 (with 66RB)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -13703,12 +13703,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -13748,17 +13748,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13773,12 +13773,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -13813,17 +13813,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -13883,17 +13883,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -13908,12 +13908,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -13953,17 +13953,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -14018,17 +14018,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -14088,17 +14088,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14113,12 +14113,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NIX</t>
+          <t>Switch 61</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -14158,17 +14158,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>SW127, NIX</t>
+          <t>Switch 63, Switch 61</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -14218,17 +14218,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S4-5</t>
+          <t>66RB</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SW138 (with S4-4)</t>
+          <t>Switch 65 (with 66RA)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SW127</t>
+          <t>Switch 63</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SW127, NIX</t>
+          <t>Switch 63, Switch 61</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -14278,12 +14278,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>62L</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SW138, NIX</t>
+          <t>Switch 65, Switch 61</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -14333,12 +14333,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>62L</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SW138</t>
+          <t>Switch 65</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14353,7 +14353,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>SW138, NIX</t>
+          <t>Switch 65, Switch 61</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>S4-7</t>
+          <t>68R</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SW129</t>
+          <t>Switch 67</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>SW129, NIX</t>
+          <t>Switch 67, Switch 61</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S4-7</t>
+          <t>68R</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SW129</t>
+          <t>Switch 67</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>SW129, NIX</t>
+          <t>Switch 67, Switch 61</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S5-1</t>
+          <t>70L</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S5-1</t>
+          <t>70L</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S5-1</t>
+          <t>70L</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S5-2</t>
+          <t>72L</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S5-2</t>
+          <t>72L</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S5-2</t>
+          <t>72L</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -14946,12 +14946,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -15006,12 +15006,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15071,12 +15071,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -15196,12 +15196,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -15261,12 +15261,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -15361,7 +15361,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S5-3</t>
+          <t>74L</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S5-4</t>
+          <t>74RA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S5-4</t>
+          <t>74RA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -15566,12 +15566,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S5-4</t>
+          <t>74RA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -15636,12 +15636,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S5-4</t>
+          <t>74RA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -15706,12 +15706,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S5-4</t>
+          <t>74RA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -15766,12 +15766,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S5-4</t>
+          <t>74RA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -15831,12 +15831,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -15896,12 +15896,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -15961,12 +15961,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -16031,12 +16031,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -16166,12 +16166,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -16236,12 +16236,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -16306,12 +16306,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S5-5</t>
+          <t>70RA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -16431,12 +16431,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -16476,12 +16476,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S5-6</t>
+          <t>70RB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DJE reverse</t>
+          <t>Switch 69 reverse</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -16501,12 +16501,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S5-6</t>
+          <t>70RB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DJE reverse</t>
+          <t>Switch 69 reverse</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -16566,12 +16566,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -16611,12 +16611,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S5-6</t>
+          <t>70RB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DJE reverse</t>
+          <t>Switch 69 reverse</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16636,12 +16636,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -16681,12 +16681,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S5-6</t>
+          <t>70RB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DJE reverse</t>
+          <t>Switch 69 reverse</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -16741,12 +16741,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S5-6</t>
+          <t>70RB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DJE reverse</t>
+          <t>Switch 69 reverse</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -16806,12 +16806,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S5-6</t>
+          <t>70RB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DJE reverse</t>
+          <t>Switch 69 reverse</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -16871,12 +16871,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S5-7</t>
+          <t>74RB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SW124 reverse</t>
+          <t>Switch 73 reverse</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -16896,12 +16896,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S5-7</t>
+          <t>74RB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SW124 reverse</t>
+          <t>Switch 73 reverse</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -16966,12 +16966,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -17016,12 +17016,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S5-7</t>
+          <t>74RB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SW124 reverse</t>
+          <t>Switch 73 reverse</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -17041,12 +17041,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DJW</t>
+          <t>Switch 71</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -17091,12 +17091,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S5-7</t>
+          <t>74RB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SW124 reverse</t>
+          <t>Switch 73 reverse</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -17116,12 +17116,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S5-7</t>
+          <t>74RB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SW124 reverse</t>
+          <t>Switch 73 reverse</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -17181,12 +17181,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -17226,12 +17226,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S5-7</t>
+          <t>74RB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SW124 reverse</t>
+          <t>Switch 73 reverse</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -17251,12 +17251,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SW124</t>
+          <t>Switch 73</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DJE</t>
+          <t>Switch 69</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -17357,47 +17357,47 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>CBX</t>
+          <t>Switch 75</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SW143</t>
+          <t>Switch 77</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SW144</t>
+          <t>Switch 79</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>SW145</t>
+          <t>Switch 81</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>SW146</t>
+          <t>Switch 83</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SW147</t>
+          <t>Switch 85</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SW148</t>
+          <t>Switch 87</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
-          <t>SW149</t>
+          <t>Switch 89</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
-          <t>SW150</t>
+          <t>Switch 91</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -18269,7 +18269,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>S6-1</t>
+          <t>76L</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>76R</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -19469,7 +19469,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S6-3</t>
+          <t>78L</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S6-3</t>
+          <t>78L</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S6-3</t>
+          <t>78L</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -19629,7 +19629,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S6-4</t>
+          <t>78RA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S6-4</t>
+          <t>78RA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S6-4</t>
+          <t>78RA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S6-4</t>
+          <t>78RA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S6-4</t>
+          <t>78RA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S6-4</t>
+          <t>78RA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -20229,7 +20229,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>S6-5</t>
+          <t>78RB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>S6-6</t>
+          <t>78R</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>S6-6</t>
+          <t>78R</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S6-6</t>
+          <t>78R</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>S6-6</t>
+          <t>78R</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>S6-6</t>
+          <t>78R</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>S6-6</t>
+          <t>78R</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S6-7</t>
+          <t>88L</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S6-7</t>
+          <t>88L</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S6-7</t>
+          <t>88L</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S6-8</t>
+          <t>88R</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S6-8</t>
+          <t>88R</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S6-8</t>
+          <t>88R</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S6-9</t>
+          <t>88RA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S6-9</t>
+          <t>88RA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S6-9</t>
+          <t>88RA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -21319,12 +21319,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S6-10</t>
+          <t>82L</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SW144</t>
+          <t>Switch 79</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -21359,12 +21359,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>S6-10</t>
+          <t>82L</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SW144</t>
+          <t>Switch 79</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -21399,12 +21399,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>S6-10</t>
+          <t>82L</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SW145</t>
+          <t>Switch 81</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -21439,12 +21439,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>S6-10</t>
+          <t>82L</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SW145</t>
+          <t>Switch 81</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -21479,12 +21479,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S6-11</t>
+          <t>84RA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SW146</t>
+          <t>Switch 83</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -21519,12 +21519,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>S6-11</t>
+          <t>84RA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SW146</t>
+          <t>Switch 83</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -21559,12 +21559,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>S6-11</t>
+          <t>84RA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SW147</t>
+          <t>Switch 85</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>S6-12</t>
+          <t>84RB</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SW147</t>
+          <t>Switch 85</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -21639,12 +21639,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S6-13</t>
+          <t>86L</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SW148</t>
+          <t>Switch 87</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -21679,12 +21679,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S6-13</t>
+          <t>86L</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SW148</t>
+          <t>Switch 87</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -21719,12 +21719,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S6-14</t>
+          <t>90L</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SW149</t>
+          <t>Switch 89</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -21759,12 +21759,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S6-14</t>
+          <t>90L</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SW149</t>
+          <t>Switch 89</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>S6-15</t>
+          <t>92L</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SW150</t>
+          <t>Switch 91</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -21839,12 +21839,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>S6-15</t>
+          <t>92L</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SW150</t>
+          <t>Switch 91</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
